--- a/02_HRvLR_groups/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/02_HRvLR_groups/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -39,7 +39,7 @@
     <t>pca_proteome</t>
   </si>
   <si>
-    <t>Panel c, left: PC1 and PC2 per sample (02_Contrasts, pca).</t>
+    <t>Panel c, left: PC1 and PC2 per sample (02_DEP, pca).</t>
   </si>
   <si>
     <t>pca_phenotype</t>
@@ -51,7 +51,7 @@
     <t>permanova</t>
   </si>
   <si>
-    <t>Panel c: PERMANOVA for the proteome (time, arm) and the phenotype (time) (02_Contrasts).</t>
+    <t>Panel c: PERMANOVA for the proteome (time, arm) and the phenotype (time) (02_DEP).</t>
   </si>
   <si>
     <t>pathways</t>

--- a/02_HRvLR_groups/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/02_HRvLR_groups/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -787,7 +787,7 @@
     <t>02_HRvLR_groups/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>a427c97768bcc7bf80a6526cbc8225f6</t>
+    <t>f3294b7f02df2c8ee462be5604fcd0a5</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -796,7 +796,7 @@
     <t>02_HRvLR_groups/03_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
-    <t>068c220be1f09313a9955fa01f855602</t>
+    <t>b928dfb75f0631b92e8ffaf819778f86</t>
   </si>
   <si>
     <t>gene_sets</t>
@@ -805,7 +805,7 @@
     <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
-    <t>587e179734739b4ba3ccdf9a51c3f6c0</t>
+    <t>bc1bf66e89df936e164c317354990470</t>
   </si>
   <si>
     <t>00_Input/phenotype.csv</t>

--- a/02_HRvLR_groups/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/02_HRvLR_groups/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -166,7 +166,7 @@
     <t>arm</t>
   </si>
   <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster arc.</t>
+    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
   </si>
   <si>
     <t>timepoint</t>
@@ -787,7 +787,7 @@
     <t>02_HRvLR_groups/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>f3294b7f02df2c8ee462be5604fcd0a5</t>
+    <t>e02599bb8f2c5a55f975346edd987fb0</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -802,7 +802,7 @@
     <t>gene_sets</t>
   </si>
   <si>
-    <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
+    <t>01_Processing/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
     <t>bc1bf66e89df936e164c317354990470</t>

--- a/02_HRvLR_groups/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/02_HRvLR_groups/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -787,7 +787,7 @@
     <t>02_HRvLR_groups/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>e02599bb8f2c5a55f975346edd987fb0</t>
+    <t>0d6cf853ff8d0d35c8767a6734aeecb9</t>
   </si>
   <si>
     <t>set_tests</t>
